--- a/artfynd/A 59368-2023 artfynd.xlsx
+++ b/artfynd/A 59368-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59368-2023 artfynd.xlsx
+++ b/artfynd/A 59368-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113396924</v>
+        <v>113396856</v>
       </c>
       <c r="B2" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,11 +703,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573743</v>
+        <v>573778</v>
       </c>
       <c r="R2" t="n">
-        <v>6421330</v>
+        <v>6421356</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113397057</v>
+        <v>113396867</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,7 +809,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -838,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573668</v>
+        <v>573762</v>
       </c>
       <c r="R3" t="n">
-        <v>6421256</v>
+        <v>6421336</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,15 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113396940</v>
+        <v>113396891</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,7 +921,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -953,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573741</v>
+        <v>573726</v>
       </c>
       <c r="R4" t="n">
-        <v>6421323</v>
+        <v>6421348</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,15 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113397015</v>
+        <v>113396918</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,7 +1031,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1068,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573756</v>
+        <v>573742</v>
       </c>
       <c r="R5" t="n">
-        <v>6421258</v>
+        <v>6421349</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,15 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113396949</v>
+        <v>113396924</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1139,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1179,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573742</v>
+        <v>573743</v>
       </c>
       <c r="R6" t="n">
-        <v>6421311</v>
+        <v>6421330</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,15 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113397031</v>
+        <v>113396932</v>
       </c>
       <c r="B7" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573708</v>
+        <v>573758</v>
       </c>
       <c r="R7" t="n">
-        <v>6421256</v>
+        <v>6421318</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,15 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113396918</v>
+        <v>113396940</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1405,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573742</v>
+        <v>573741</v>
       </c>
       <c r="R8" t="n">
-        <v>6421349</v>
+        <v>6421323</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1468,15 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113396891</v>
+        <v>113396949</v>
       </c>
       <c r="B9" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,11 +1465,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1520,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573726</v>
+        <v>573742</v>
       </c>
       <c r="R9" t="n">
-        <v>6421348</v>
+        <v>6421311</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,6 +1540,1506 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113396957</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 59368, Källarhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>573773</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6421335</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113396963</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 59368, Källarhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>573758</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6421300</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>113396969</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 59368, Källarhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>573755</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6421312</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>113396975</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 59368, Källarhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>573750</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6421283</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>113396987</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A 59368, Källarhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>573768</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6421268</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>113396994</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>A 59368, Källarhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>573756</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6421274</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>113397000</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A 59368, Källarhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>573767</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6421269</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>113397015</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>A 59368, Källarhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>573756</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6421258</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>113397023</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>A 59368, Källarhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>573726</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6421241</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>113397031</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 59368, Källarhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>573708</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6421256</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>113397039</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A 59368, Källarhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>573708</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6421242</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>113397046</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A 59368, Källarhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>573717</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6421240</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>113397049</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A 59368, Källarhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>573708</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6421252</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>113397057</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>A 59368, Källarhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>573668</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6421256</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
